--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487169_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487169_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. LOPEZ BRETON</t>
+          <t>A. KARATZAS LACABEX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0664</v>
+        <v>3.2936</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1389</v>
+        <v>4.7516</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.0725</v>
+        <v>-1.4581</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7392</v>
+        <v>4.9624</v>
       </c>
       <c r="H2" t="n">
-        <v>3.555</v>
+        <v>3.6308</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1842</v>
+        <v>1.3316</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9678</v>
+        <v>6.8773</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5434</v>
+        <v>4.3054</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4245</v>
+        <v>2.5719</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.2286</v>
+        <v>-1.9149</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9883</v>
+        <v>-0.6747</v>
       </c>
       <c r="O2" t="n">
         <v>-1.2403</v>
       </c>
       <c r="P2" t="n">
-        <v>0.579</v>
+        <v>-1.3511</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.158</v>
+        <v>-3.0881</v>
       </c>
       <c r="R2" t="n">
         <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6082</v>
+        <v>1.0245</v>
       </c>
       <c r="T2" t="n">
-        <v>1.17</v>
+        <v>0.9624</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4382</v>
+        <v>0.0621</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.8601</v>
+        <v>-1.3423</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1591</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.0192</v>
+        <v>-1.3423</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. KARATZAS LACABEX</t>
+          <t>A. LOPEZ BRETON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0477</v>
+        <v>2.645</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2916</v>
+        <v>5.7978</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2439</v>
+        <v>-3.1528</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9624</v>
+        <v>3.7392</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6308</v>
+        <v>3.555</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3316</v>
+        <v>0.1842</v>
       </c>
       <c r="J3" t="n">
-        <v>6.8773</v>
+        <v>5.9678</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3054</v>
+        <v>4.5434</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5719</v>
+        <v>1.4245</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9149</v>
+        <v>-2.2286</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6747</v>
+        <v>-0.9883</v>
       </c>
       <c r="O3" t="n">
         <v>-1.2403</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3511</v>
+        <v>0.579</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0881</v>
+        <v>-1.158</v>
       </c>
       <c r="R3" t="n">
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7786</v>
+        <v>1.1868</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5024</v>
+        <v>0.8289</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2763</v>
+        <v>0.3579</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.3423</v>
+        <v>-2.8601</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.1591</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3423</v>
+        <v>-3.0192</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9543</v>
+        <v>2.0544</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5088</v>
+        <v>1.6089</v>
       </c>
       <c r="F4" t="n">
         <v>0.4455</v>
@@ -766,10 +766,10 @@
         <v>0.386</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.1001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0595</v>
+        <v>0.0407</v>
       </c>
       <c r="U4" t="n">
         <v>0.0595</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3766</v>
+        <v>1.2173</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6273</v>
+        <v>1.3878</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2508</v>
+        <v>-0.1705</v>
       </c>
       <c r="G5" t="n">
         <v>0.3866</v>
@@ -844,13 +844,13 @@
         <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.466</v>
+        <v>0.3748</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4759</v>
+        <v>0.2846</v>
       </c>
       <c r="U5" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0902</v>
       </c>
       <c r="V5" t="n">
         <v>1.228</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. AZKOAGA BENDEJACQ</t>
+          <t>G. HUESO GUTIERREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4836</v>
+        <v>0.5216</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3824</v>
+        <v>3.2628</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1011</v>
+        <v>-2.7412</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1926</v>
+        <v>1.0315</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2918</v>
+        <v>-0.8571</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0993</v>
+        <v>1.8886</v>
       </c>
       <c r="J6" t="n">
-        <v>0.346</v>
+        <v>2.319</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3053</v>
+        <v>-0.2693</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0407</v>
+        <v>2.5883</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1534</v>
+        <v>-1.2875</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0134</v>
+        <v>-0.5878</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.14</v>
+        <v>-0.6998</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.158</v>
       </c>
       <c r="R6" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2816</v>
+        <v>0.6973</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4297</v>
+        <v>0.8739</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1481</v>
+        <v>-0.1765</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5717</v>
+        <v>-1.0142</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5717</v>
+        <v>-2.2422</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. HUESO GUTIERREZ</t>
+          <t>A. AZKOAGA BENDEJACQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6543</v>
+        <v>-0.784</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4617</v>
+        <v>-0.6829</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.1159</v>
+        <v>-0.1011</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0315</v>
+        <v>0.1926</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8571</v>
+        <v>0.2918</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8886</v>
+        <v>-0.0993</v>
       </c>
       <c r="J7" t="n">
-        <v>2.319</v>
+        <v>0.346</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2693</v>
+        <v>0.3053</v>
       </c>
       <c r="L7" t="n">
-        <v>2.5883</v>
+        <v>0.0407</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2875</v>
+        <v>-0.1534</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5878</v>
+        <v>-0.0134</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6998</v>
+        <v>-0.14</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.158</v>
       </c>
       <c r="R7" t="n">
-        <v>0.965</v>
+        <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4785</v>
+        <v>-0.0188</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0727</v>
+        <v>0.1292</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5513</v>
+        <v>-0.1481</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0142</v>
+        <v>-0.5717</v>
       </c>
       <c r="W7" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2422</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ ORTEGA</t>
+          <t>P. MOLINA MATA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5895</v>
+        <v>-1.9683</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5963</v>
+        <v>-0.5734</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1859</v>
+        <v>-1.3949</v>
       </c>
       <c r="G8" t="n">
-        <v>0.875</v>
+        <v>-0.7015</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2006</v>
+        <v>0.4545</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3256</v>
+        <v>-1.156</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8097</v>
+        <v>-0.0076</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3959</v>
+        <v>1.2626</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-1.2702</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9347</v>
+        <v>-0.694</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1953</v>
+        <v>-0.8082</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2606</v>
+        <v>0.1142</v>
       </c>
       <c r="P8" t="n">
-        <v>0.386</v>
+        <v>1.5441</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3511</v>
+        <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2843</v>
+        <v>-0.8461</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4079</v>
+        <v>-0.3728</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1236</v>
+        <v>-0.4733</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.1348</v>
+        <v>-1.9647</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.4786</v>
+        <v>-1.9647</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3366</v>
+        <v>-2.6043</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9191</v>
+        <v>-1.16</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4175</v>
+        <v>-1.4443</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5737</v>
@@ -1156,13 +1156,13 @@
         <v>2.5091</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0112</v>
+        <v>-0.2565</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4429</v>
+        <v>0.202</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4316</v>
+        <v>-0.4584</v>
       </c>
       <c r="V9" t="n">
         <v>1.7698</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MOLINA MATA</t>
+          <t>A. FERNANDEZ ORTEGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.809</v>
+        <v>-2.6514</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0929</v>
+        <v>0.4541</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7161</v>
+        <v>-3.1055</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7015</v>
+        <v>0.875</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4545</v>
+        <v>1.2006</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.156</v>
+        <v>-0.3256</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0076</v>
+        <v>1.8097</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2626</v>
+        <v>2.3959</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2702</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.694</v>
+        <v>-0.9347</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8082</v>
+        <v>-1.1953</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1142</v>
+        <v>0.2606</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6868</v>
+        <v>0.2224</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8923</v>
+        <v>0.2657</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7945</v>
+        <v>-0.0433</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.9647</v>
+        <v>-4.1348</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.9647</v>
+        <v>-3.4786</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8666</v>
+        <v>-3.9969</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8506</v>
+        <v>-1.3919</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0161</v>
+        <v>-2.605</v>
       </c>
       <c r="G11" t="n">
         <v>-3.2719</v>
@@ -1312,13 +1312,13 @@
         <v>1.3511</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9843</v>
+        <v>0.854</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4079</v>
+        <v>0.8666</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5763</v>
+        <v>-0.0126</v>
       </c>
       <c r="V11" t="n">
         <v>-0.614</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.744</v>
+        <v>-4.1709</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6611</v>
+        <v>-3.1416</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0829</v>
+        <v>-1.0293</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0509</v>
@@ -1390,13 +1390,13 @@
         <v>2.5091</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5737</v>
+        <v>-0.0007</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4627</v>
+        <v>0.0569</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1111</v>
+        <v>-0.0575</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5054</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.0386</v>
+        <v>-6.443899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>9.718499999999997</v>
+        <v>10.3132</v>
       </c>
       <c r="F13" t="n">
         <v>-16.7572</v>
@@ -1453,7 +1453,7 @@
         <v>-13.8458</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.580299999999999</v>
+        <v>-7.580300000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-6.265899999999999</v>
@@ -1468,13 +1468,13 @@
         <v>15.4407</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7432</v>
+        <v>3.3378</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5431</v>
+        <v>4.1381</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8</v>
+        <v>-0.7999999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-10.7235</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.439</v>
+        <v>9.276</v>
       </c>
       <c r="E14" t="n">
-        <v>8.5869</v>
+        <v>7.9861</v>
       </c>
       <c r="F14" t="n">
-        <v>1.852</v>
+        <v>1.2899</v>
       </c>
       <c r="G14" t="n">
         <v>1.8492</v>
@@ -1546,13 +1546,13 @@
         <v>3.2811</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0675</v>
+        <v>-0.0955</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1396</v>
+        <v>0.5387</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0721</v>
+        <v>-0.6343</v>
       </c>
       <c r="V14" t="n">
         <v>5.2062</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.6974</v>
+        <v>8.9978</v>
       </c>
       <c r="E15" t="n">
-        <v>7.9672</v>
+        <v>8.2676</v>
       </c>
       <c r="F15" t="n">
         <v>0.7302</v>
@@ -1624,10 +1624,10 @@
         <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8752</v>
+        <v>-0.5747</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4614</v>
+        <v>-0.1609</v>
       </c>
       <c r="U15" t="n">
         <v>-0.4138</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0453</v>
+        <v>3.1256</v>
       </c>
       <c r="E16" t="n">
         <v>2.7329</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3124</v>
+        <v>0.3927</v>
       </c>
       <c r="G16" t="n">
         <v>0.4406</v>
@@ -1702,13 +1702,13 @@
         <v>2.3161</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5546</v>
+        <v>-0.4743</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1507</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4039</v>
+        <v>-0.3236</v>
       </c>
       <c r="V16" t="n">
         <v>1.8082</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0187</v>
+        <v>-0.1119</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7832</v>
+        <v>0.5829</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.6948</v>
       </c>
       <c r="G17" t="n">
         <v>-2.2017</v>
@@ -1780,13 +1780,13 @@
         <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3675</v>
+        <v>0.2743</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5632</v>
+        <v>0.3629</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="V17" t="n">
         <v>1.2364</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1867</v>
+        <v>-1.2938</v>
       </c>
       <c r="E18" t="n">
         <v>-1.0034</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1833</v>
+        <v>-0.2904</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3128</v>
@@ -1858,13 +1858,13 @@
         <v>2.7021</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7231</v>
+        <v>-0.8302</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0912</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6319</v>
+        <v>-0.739</v>
       </c>
       <c r="V18" t="n">
         <v>0.0422</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3226</v>
+        <v>-1.6613</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4069</v>
+        <v>-1.9062</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0844</v>
+        <v>0.245</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2051</v>
@@ -1936,13 +1936,13 @@
         <v>2.5091</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0801</v>
+        <v>-0.4187</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6993</v>
+        <v>-0.1986</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3808</v>
+        <v>-0.2201</v>
       </c>
       <c r="V19" t="n">
         <v>1.2787</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. GANDARILLAS GARMENDIA</t>
+          <t>L. MAESTRO STEELE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0528</v>
+        <v>-2.88</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1864</v>
+        <v>1.0232</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.2392</v>
+        <v>-3.9032</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6083</v>
+        <v>-4.079</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1478</v>
+        <v>-1.2201</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4606</v>
+        <v>-2.8589</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5404</v>
+        <v>0.3058</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2329</v>
+        <v>1.511</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7733</v>
+        <v>-1.2052</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1487</v>
+        <v>-4.3848</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9149</v>
+        <v>-2.7312</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2338</v>
+        <v>-1.6537</v>
       </c>
       <c r="P20" t="n">
-        <v>-0</v>
+        <v>1.5441</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>0.965</v>
+        <v>2.5091</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5023</v>
+        <v>-0.6309</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3252</v>
+        <v>0.1686</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8276</v>
+        <v>-0.7995</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9421</v>
+        <v>0.2859</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="X20" t="n">
         <v>-1.228</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. MAESTRO STEELE</t>
+          <t>E. GANDARILLAS GARMENDIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2677</v>
+        <v>-2.9923</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8229</v>
+        <v>0.0863</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.0906</v>
+        <v>-3.0786</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.079</v>
+        <v>-1.6083</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2201</v>
+        <v>-1.1478</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.8589</v>
+        <v>-0.4606</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3058</v>
+        <v>0.5404</v>
       </c>
       <c r="K21" t="n">
-        <v>1.511</v>
+        <v>-0.2329</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2052</v>
+        <v>0.7733</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.3848</v>
+        <v>-2.1487</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.7312</v>
+        <v>-0.9149</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6537</v>
+        <v>-1.2338</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5441</v>
+        <v>-0</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5091</v>
+        <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0186</v>
+        <v>-0.4419</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0317</v>
+        <v>0.2251</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9869</v>
+        <v>-0.6669</v>
       </c>
       <c r="V21" t="n">
+        <v>-0.9421</v>
+      </c>
+      <c r="W21" t="n">
         <v>0.2859</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.5138</v>
       </c>
       <c r="X21" t="n">
         <v>-1.228</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2943</v>
+        <v>-5.4212</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9118000000000001</v>
+        <v>-1.0119</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.3825</v>
+        <v>-4.4093</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4345</v>
@@ -2170,13 +2170,13 @@
         <v>0.965</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5757</v>
+        <v>0.4488</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2062</v>
+        <v>0.1061</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3695</v>
+        <v>0.3427</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5054</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.038900000000003</v>
+        <v>7.038900000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>16.7574</v>
+        <v>16.7575</v>
       </c>
       <c r="F23" t="n">
-        <v>-9.718500000000001</v>
+        <v>-9.718499999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-2.871700000000001</v>
@@ -2248,13 +2248,13 @@
         <v>17.3706</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.7432</v>
+        <v>-2.7431</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.543200000000001</v>
+        <v>-3.5431</v>
       </c>
       <c r="V23" t="n">
         <v>10.7236</v>
